--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486266_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486266_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8273</v>
+        <v>3.6376</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7159</v>
+        <v>4.7728</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-1.1351</v>
       </c>
       <c r="G2" t="n">
         <v>1.4205</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5368</v>
+        <v>1.3471</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7219</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.5684</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3932</v>
+        <v>0.7238</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1916</v>
+        <v>1.7071</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7983</v>
+        <v>-0.9832</v>
       </c>
       <c r="G3" t="n">
         <v>-1.4937</v>
@@ -688,13 +688,13 @@
         <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0053</v>
+        <v>-0.6748</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8099</v>
+        <v>-0.2944</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1954</v>
+        <v>-0.3803</v>
       </c>
       <c r="V3" t="n">
         <v>0.9347</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2221</v>
+        <v>0.1007</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.284</v>
+        <v>0.008</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0619</v>
+        <v>0.0927</v>
       </c>
       <c r="G4" t="n">
         <v>-1.3858</v>
@@ -766,13 +766,13 @@
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1011</v>
+        <v>0.4239</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1646</v>
+        <v>0.4567</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0636</v>
+        <v>-0.0328</v>
       </c>
       <c r="V4" t="n">
         <v>3.0202</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.3982</v>
+        <v>-0.2152</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4575</v>
+        <v>2.2398</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8557</v>
+        <v>-2.455</v>
       </c>
       <c r="G5" t="n">
         <v>-2.2523</v>
@@ -844,13 +844,13 @@
         <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4933</v>
+        <v>-0.3103</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0719</v>
+        <v>-0.2896</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4214</v>
+        <v>-0.0207</v>
       </c>
       <c r="V5" t="n">
         <v>1.695</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3196</v>
+        <v>-1.253</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8507</v>
+        <v>0.0001</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4688</v>
+        <v>-1.2531</v>
       </c>
       <c r="G6" t="n">
         <v>-3.0334</v>
@@ -922,13 +922,13 @@
         <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5037</v>
+        <v>-0.4371</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5924</v>
+        <v>0.2584</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9113</v>
+        <v>-0.6955</v>
       </c>
       <c r="V6" t="n">
         <v>1.13</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.2732</v>
+        <v>-4.0034</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.2143</v>
+        <v>-3.5438</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0589</v>
+        <v>-0.4596</v>
       </c>
       <c r="G7" t="n">
         <v>-5.8775</v>
@@ -1000,13 +1000,13 @@
         <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4743</v>
+        <v>0.7442</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6609</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1352</v>
+        <v>0.7345</v>
       </c>
       <c r="V7" t="n">
         <v>1.13</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.9447</v>
+        <v>-4.8215</v>
       </c>
       <c r="E8" t="n">
         <v>-3.7794</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1653</v>
+        <v>-1.042</v>
       </c>
       <c r="G8" t="n">
         <v>-2.1256</v>
@@ -1078,13 +1078,13 @@
         <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5343</v>
+        <v>-0.411</v>
       </c>
       <c r="T8" t="n">
         <v>0.2896</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8239</v>
+        <v>-0.7006</v>
       </c>
       <c r="V8" t="n">
         <v>0.7602</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.4497</v>
+        <v>-5.836</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.4859</v>
+        <v>-5.0879</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9638</v>
+        <v>-0.748</v>
       </c>
       <c r="G9" t="n">
         <v>-5.7582</v>
@@ -1156,13 +1156,13 @@
         <v>1.9576</v>
       </c>
       <c r="S9" t="n">
-        <v>0.526</v>
+        <v>0.1397</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2007</v>
+        <v>-0.4014</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3253</v>
+        <v>0.5411</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.1376</v>
+        <v>-7.5152</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7391</v>
+        <v>-4.9626</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3985</v>
+        <v>-2.5526</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5364</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1388</v>
+        <v>-0.2388</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1454</v>
+        <v>-0.3689</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2842</v>
+        <v>0.1301</v>
       </c>
       <c r="V10" t="n">
         <v>-1.13</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-19.5246</v>
+        <v>-19.1822</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.988399999999999</v>
+        <v>-8.645899999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-10.536</v>
+        <v>-10.5359</v>
       </c>
       <c r="G11" t="n">
         <v>-24.0424</v>
@@ -1312,13 +1312,13 @@
         <v>15.2256</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2403999999999997</v>
+        <v>0.5829000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09630000000000002</v>
+        <v>0.4387000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1441</v>
+        <v>0.1442000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>7.540100000000002</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.146599999999999</v>
+        <v>10.0766</v>
       </c>
       <c r="E12" t="n">
-        <v>5.527</v>
+        <v>5.974</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6196</v>
+        <v>4.1026</v>
       </c>
       <c r="G12" t="n">
         <v>10.5134</v>
@@ -1390,13 +1390,13 @@
         <v>2.6101</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7143</v>
+        <v>0.2157</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8904</v>
+        <v>-0.4434</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1762</v>
+        <v>0.6591</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>C. ROGERS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.0802</v>
+        <v>6.3625</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7072</v>
+        <v>4.2931</v>
       </c>
       <c r="F13" t="n">
-        <v>1.373</v>
+        <v>2.0695</v>
       </c>
       <c r="G13" t="n">
-        <v>5.7064</v>
+        <v>6.3486</v>
       </c>
       <c r="H13" t="n">
-        <v>4.492</v>
+        <v>3.303</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2144</v>
+        <v>3.0456</v>
       </c>
       <c r="J13" t="n">
-        <v>5.1711</v>
+        <v>5.0658</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8324</v>
+        <v>2.5763</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3387</v>
+        <v>2.4894</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5354</v>
+        <v>1.2828</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6597</v>
+        <v>0.7267</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1243</v>
+        <v>0.5562</v>
       </c>
       <c r="P13" t="n">
-        <v>0.87</v>
+        <v>2.3926</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1751</v>
+        <v>2.6101</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2639</v>
+        <v>-0.1187</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2762</v>
+        <v>-0.5552</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0123</v>
+        <v>0.4365</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.7602</v>
+        <v>-2.2599</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.3252</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. ROGERS</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4159</v>
+        <v>6.199</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9578</v>
+        <v>4.5897</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4581</v>
+        <v>1.6093</v>
       </c>
       <c r="G14" t="n">
-        <v>6.3486</v>
+        <v>5.7064</v>
       </c>
       <c r="H14" t="n">
-        <v>3.303</v>
+        <v>4.492</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0456</v>
+        <v>1.2144</v>
       </c>
       <c r="J14" t="n">
-        <v>5.0658</v>
+        <v>5.1711</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5763</v>
+        <v>3.8324</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4894</v>
+        <v>1.3387</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2828</v>
+        <v>0.5354</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7267</v>
+        <v>0.6597</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5562</v>
+        <v>-0.1243</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3926</v>
+        <v>0.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R14" t="n">
-        <v>2.6101</v>
+        <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0653</v>
+        <v>0.3827</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8904</v>
+        <v>0.1586</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1749</v>
+        <v>0.2241</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.2599</v>
+        <v>-0.7602</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.2599</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.783</v>
+        <v>4.2794</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4615</v>
+        <v>2.5675</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3214</v>
+        <v>1.7119</v>
       </c>
       <c r="G15" t="n">
         <v>2.5869</v>
@@ -1624,13 +1624,13 @@
         <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9557</v>
+        <v>0.4521</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5502</v>
+        <v>0.6561</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5945</v>
+        <v>-0.204</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9347</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0455</v>
+        <v>2.0018</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5543</v>
+        <v>-0.7779</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5998</v>
+        <v>2.7796</v>
       </c>
       <c r="G16" t="n">
         <v>0.8314</v>
@@ -1702,13 +1702,13 @@
         <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>0.649</v>
+        <v>0.6054</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1286</v>
+        <v>-0.0949</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5204</v>
+        <v>0.7003</v>
       </c>
       <c r="V16" t="n">
         <v>0.5649999999999999</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2625</v>
+        <v>0.2652</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6831</v>
+        <v>-1.4596</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9457</v>
+        <v>1.7248</v>
       </c>
       <c r="G17" t="n">
         <v>1.1697</v>
@@ -1780,13 +1780,13 @@
         <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3098</v>
+        <v>0.3124</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.822</v>
+        <v>-0.5984</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1317</v>
+        <v>0.9109</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8695</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8507</v>
+        <v>-0.9252</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-1.1958</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1216</v>
+        <v>0.2706</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8812</v>
@@ -1858,13 +1858,13 @@
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.274</v>
+        <v>-0.3485</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1286</v>
+        <v>-0.0949</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4026</v>
+        <v>-0.2536</v>
       </c>
       <c r="V18" t="n">
         <v>0.7395</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PERIS CRESPO</t>
+          <t>J. ROUND</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4647</v>
+        <v>-1.39</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4858</v>
+        <v>-0.9755</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9789</v>
+        <v>-0.4144</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1643</v>
+        <v>-1.4918</v>
       </c>
       <c r="H19" t="n">
-        <v>3.0872</v>
+        <v>0.2493</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9228</v>
+        <v>-1.7412</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8506</v>
+        <v>-0.3531</v>
       </c>
       <c r="K19" t="n">
-        <v>3.288</v>
+        <v>-0.5443</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4374</v>
+        <v>0.1912</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6863</v>
+        <v>-1.1388</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2009</v>
+        <v>0.7936</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4854</v>
+        <v>-1.9324</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4801</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8667</v>
+        <v>0.2971</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6165</v>
+        <v>0.4651</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2502</v>
+        <v>-0.1679</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3698</v>
+        <v>-0.1952</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. ROUND</t>
+          <t>J. PERIS CRESPO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5743</v>
+        <v>-1.8185</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6461</v>
+        <v>0.073</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9282</v>
+        <v>-1.8915</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4918</v>
+        <v>1.1643</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2493</v>
+        <v>3.0872</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7412</v>
+        <v>-1.9228</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3531</v>
+        <v>2.8506</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5443</v>
+        <v>3.288</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1912</v>
+        <v>-0.4374</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1388</v>
+        <v>-1.6863</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7936</v>
+        <v>-0.2009</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.9324</v>
+        <v>-1.4854</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>-3.4801</v>
       </c>
       <c r="R20" t="n">
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8872</v>
+        <v>-0.2205</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2055</v>
+        <v>-0.0577</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6817</v>
+        <v>-0.1628</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1952</v>
+        <v>-0.3698</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3196</v>
+        <v>-3.2912</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.776</v>
+        <v>-2.5525</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5436</v>
+        <v>-0.7387</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9055</v>
@@ -2092,13 +2092,13 @@
         <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3886</v>
+        <v>0.417</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1971</v>
+        <v>0.4206</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1915</v>
+        <v>-0.0036</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4552</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>19.5244</v>
+        <v>21.7596</v>
       </c>
       <c r="E22" t="n">
-        <v>10.5359</v>
+        <v>10.536</v>
       </c>
       <c r="F22" t="n">
-        <v>8.9885</v>
+        <v>11.2237</v>
       </c>
       <c r="G22" t="n">
         <v>24.0422</v>
@@ -2140,7 +2140,7 @@
         <v>15.1017</v>
       </c>
       <c r="I22" t="n">
-        <v>8.9405</v>
+        <v>8.940499999999998</v>
       </c>
       <c r="J22" t="n">
         <v>23.2347</v>
@@ -2158,7 +2158,7 @@
         <v>5.0313</v>
       </c>
       <c r="O22" t="n">
-        <v>-4.2234</v>
+        <v>-4.223400000000001</v>
       </c>
       <c r="P22" t="n">
         <v>3.2626</v>
@@ -2170,13 +2170,13 @@
         <v>18.4882</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2404999999999999</v>
+        <v>1.9947</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1441</v>
+        <v>-0.1441000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.09640000000000026</v>
+        <v>2.139000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-7.539999999999999</v>
